--- a/results/canaliculi/682_z08c1-2/measurements.xlsx
+++ b/results/canaliculi/682_z08c1-2/measurements.xlsx
@@ -433,6 +433,11 @@
           <t>interior_lacuna_count</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>assignment_method</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -446,6 +451,11 @@
       <c r="C2" t="n">
         <v>8</v>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>graph</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -493,13 +503,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59.375</v>
+        <v>41</v>
       </c>
       <c r="C6" t="n">
-        <v>39</v>
+        <v>30.5</v>
       </c>
       <c r="D6" t="n">
-        <v>46.0743</v>
+        <v>21.1458</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -517,13 +527,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>209.1722</v>
+        <v>118.8547</v>
       </c>
       <c r="C7" t="n">
-        <v>181.8005</v>
+        <v>120.8246</v>
       </c>
       <c r="D7" t="n">
-        <v>107.4494</v>
+        <v>57.5649</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -585,13 +595,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>404</v>
+        <v>188</v>
       </c>
       <c r="C2" t="n">
-        <v>192448.7907</v>
+        <v>41991.0041</v>
       </c>
       <c r="D2" t="n">
-        <v>476.3584</v>
+        <v>223.3564</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -607,13 +617,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C3" t="n">
-        <v>5813.0504</v>
+        <v>2775.6013</v>
       </c>
       <c r="D3" t="n">
-        <v>138.406</v>
+        <v>86.7375</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -629,13 +639,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>155</v>
+        <v>67</v>
       </c>
       <c r="C4" t="n">
-        <v>52885.8805</v>
+        <v>9535.539000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>341.1992</v>
+        <v>142.3215</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -651,13 +661,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C5" t="n">
-        <v>29975.203</v>
+        <v>7648.8271</v>
       </c>
       <c r="D5" t="n">
-        <v>348.5489</v>
+        <v>115.8913</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -673,13 +683,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C6" t="n">
-        <v>10008.396</v>
+        <v>6199.0453</v>
       </c>
       <c r="D6" t="n">
-        <v>294.3646</v>
+        <v>229.5943</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -695,13 +705,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C7" t="n">
-        <v>3810.7182</v>
+        <v>1582.3717</v>
       </c>
       <c r="D7" t="n">
-        <v>105.8533</v>
+        <v>63.2949</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -717,13 +727,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" t="n">
-        <v>705.9554000000001</v>
+        <v>147.7401</v>
       </c>
       <c r="D8" t="n">
-        <v>70.5955</v>
+        <v>16.4156</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
@@ -739,13 +749,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="C9" t="n">
-        <v>18240.7886</v>
+        <v>8174.2669</v>
       </c>
       <c r="D9" t="n">
-        <v>225.1949</v>
+        <v>125.758</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -761,13 +771,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>1477.8398</v>
+        <v>4155.3275</v>
       </c>
       <c r="D10" t="n">
-        <v>86.9318</v>
+        <v>143.2872</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -783,13 +793,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>3189.0836</v>
+        <v>747.1981</v>
       </c>
       <c r="D11" t="n">
-        <v>132.8785</v>
+        <v>43.9528</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>

--- a/results/canaliculi/682_z08c1-2/measurements.xlsx
+++ b/results/canaliculi/682_z08c1-2/measurements.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,6 +438,16 @@
           <t>assignment_method</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>count_mode</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>preprocess_mode</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -456,91 +466,132 @@
           <t>graph</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>tophat</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>v1-raw / pre-validation -- stats below over interior (on_border=False) lacunae only</t>
+          <t>count_mode='edge': one canaliculus = one graph edge (OCY-style); 'path': one canaliculus = one cell-to-tip path (re-counts shared trunks)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>metric</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>mean</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>median</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>units</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>n</t>
+          <t>v1-raw / pre-validation -- stats below over interior (on_border=False) lacunae only</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>canaliculi_count</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>41</v>
-      </c>
-      <c r="C6" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="D6" t="n">
-        <v>21.1458</v>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>median</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>unitless</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>8</v>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>canaliculi_count</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>42.25</v>
+      </c>
+      <c r="C7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D7" t="n">
+        <v>32.5609</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>total_length_px</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1126.5241</v>
+      </c>
+      <c r="C8" t="n">
+        <v>782.9296000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>782.8783</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>mean_canaliculus_length_px</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>118.8547</v>
-      </c>
-      <c r="C7" t="n">
-        <v>120.8246</v>
-      </c>
-      <c r="D7" t="n">
-        <v>57.5649</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>px</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
+      <c r="B9" t="n">
+        <v>28.3251</v>
+      </c>
+      <c r="C9" t="n">
+        <v>26.8083</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.7491</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>8</v>
       </c>
     </row>
@@ -595,13 +646,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>188</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>41991.0041</v>
+        <v>373.9361</v>
       </c>
       <c r="D2" t="n">
-        <v>223.3564</v>
+        <v>20.7742</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -617,13 +668,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C3" t="n">
-        <v>2775.6013</v>
+        <v>1134.6194</v>
       </c>
       <c r="D3" t="n">
-        <v>86.7375</v>
+        <v>26.3865</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -639,13 +690,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>9535.539000000001</v>
+        <v>513.9432</v>
       </c>
       <c r="D4" t="n">
-        <v>142.3215</v>
+        <v>32.1215</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -661,13 +712,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>66</v>
+        <v>109</v>
       </c>
       <c r="C5" t="n">
-        <v>7648.8271</v>
+        <v>2537.6236</v>
       </c>
       <c r="D5" t="n">
-        <v>115.8913</v>
+        <v>23.281</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -683,13 +734,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
-        <v>6199.0453</v>
+        <v>520.1737000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>229.5943</v>
+        <v>24.7702</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -705,13 +756,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C7" t="n">
-        <v>1582.3717</v>
+        <v>597.3452</v>
       </c>
       <c r="D7" t="n">
-        <v>63.2949</v>
+        <v>20.5981</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -727,13 +778,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>147.7401</v>
+        <v>207.1076</v>
       </c>
       <c r="D8" t="n">
-        <v>16.4156</v>
+        <v>29.5868</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
@@ -749,13 +800,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>8174.2669</v>
+        <v>2142.6286</v>
       </c>
       <c r="D9" t="n">
-        <v>125.758</v>
+        <v>29.7587</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -771,13 +822,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>4155.3275</v>
+        <v>844.1341</v>
       </c>
       <c r="D10" t="n">
-        <v>143.2872</v>
+        <v>27.2301</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -796,10 +847,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>747.1981</v>
+        <v>721.725</v>
       </c>
       <c r="D11" t="n">
-        <v>43.9528</v>
+        <v>42.4544</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>

--- a/results/canaliculi/682_z08c1-2/measurements.xlsx
+++ b/results/canaliculi/682_z08c1-2/measurements.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="per_lacuna" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="field" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="per_lacuna" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -530,13 +531,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>42.25</v>
+        <v>76</v>
       </c>
       <c r="C7" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="D7" t="n">
-        <v>32.5609</v>
+        <v>85.157</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -554,13 +555,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1126.5241</v>
+        <v>1860.5611</v>
       </c>
       <c r="C8" t="n">
-        <v>782.9296000000001</v>
+        <v>997.753</v>
       </c>
       <c r="D8" t="n">
-        <v>782.8783</v>
+        <v>1996.4827</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -578,13 +579,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28.3251</v>
+        <v>25.4567</v>
       </c>
       <c r="C9" t="n">
-        <v>26.8083</v>
+        <v>25.0725</v>
       </c>
       <c r="D9" t="n">
-        <v>6.7491</v>
+        <v>4.7151</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -606,6 +607,206 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>per-field metrics -- independent of the per-lacuna assignment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Only ~23% of skeleton length is graph-connected to any lacuna in these 2D</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>sections, so per-cell numbers use a quarter of the network. These use all of it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>analysed_area_px2</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1017909</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>total_skeleton_length_px</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>35267</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>canalicular_length_density_per_px</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.03464652</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>junction_count</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>480</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>junction_density_per_px2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.00047155</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>px^-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>lacuna_count</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>10</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>lacunae_per_px2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>9.819999999999999e-06</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>px^-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>skeleton_component_count</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>720</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>mean_component_length_px</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>48.9819</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>median_component_length_px</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -646,13 +847,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>373.9361</v>
+        <v>480.7056</v>
       </c>
       <c r="D2" t="n">
-        <v>20.7742</v>
+        <v>22.8907</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -668,13 +869,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="C3" t="n">
-        <v>1134.6194</v>
+        <v>1236.1463</v>
       </c>
       <c r="D3" t="n">
-        <v>26.3865</v>
+        <v>23.3235</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -690,13 +891,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C4" t="n">
-        <v>513.9432</v>
+        <v>966.3768</v>
       </c>
       <c r="D4" t="n">
-        <v>32.1215</v>
+        <v>31.1734</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -712,13 +913,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>109</v>
+        <v>277</v>
       </c>
       <c r="C5" t="n">
-        <v>2537.6236</v>
+        <v>6469.8006</v>
       </c>
       <c r="D5" t="n">
-        <v>23.281</v>
+        <v>23.3567</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -734,13 +935,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
-        <v>520.1737000000001</v>
+        <v>546.4163</v>
       </c>
       <c r="D6" t="n">
-        <v>24.7702</v>
+        <v>23.7572</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -756,13 +957,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="C7" t="n">
-        <v>597.3452</v>
+        <v>940.0265000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>20.5981</v>
+        <v>16.7862</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -778,13 +979,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" t="n">
-        <v>207.1076</v>
+        <v>294.1198</v>
       </c>
       <c r="D8" t="n">
-        <v>29.5868</v>
+        <v>36.765</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
@@ -800,13 +1001,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="C9" t="n">
-        <v>2142.6286</v>
+        <v>2897.3708</v>
       </c>
       <c r="D9" t="n">
-        <v>29.7587</v>
+        <v>28.1298</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -822,13 +1023,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>844.1341</v>
+        <v>1029.1291</v>
       </c>
       <c r="D10" t="n">
-        <v>27.2301</v>
+        <v>26.3879</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -844,13 +1045,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>721.725</v>
+        <v>799.2224</v>
       </c>
       <c r="D11" t="n">
-        <v>42.4544</v>
+        <v>30.7393</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
